--- a/rules/CORE-000761/positive/01/data/unit-test-coreid-CG0289-positive.xlsx
+++ b/rules/CORE-000761/positive/01/data/unit-test-coreid-CG0289-positive.xlsx
@@ -18,9 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -554,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1265,6 +1264,51 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RANDOM</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Trial is Randomized</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>C49488</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>CDISC CT</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2021-03-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
